--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,12 +236,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -251,12 +251,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -266,22 +266,22 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0758</t>
+          <t>1.0596</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3701</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2734</t>
+          <t>0.2696</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:GOQASy66</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -510,82 +510,82 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>10411540</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>1.058</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3939</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.278</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3282</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -595,34 +595,34 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -662,77 +662,77 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10411540</t>
+          <t>10390285</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.6944</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1.0656</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.3939</t>
+          <t>0.1443</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.204</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.3282</t>
+          <t>0.6517</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -746,153 +746,6 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:56:46 ACST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>10390285</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Man City</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.2174</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.0656</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.1443</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.204</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.6517</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -1055,7 +908,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1125,12 +978,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1140,12 +993,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1155,22 +1008,22 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0758</t>
+          <t>1.0596</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.3701</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2734</t>
+          <t>0.2696</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1202,7 +1055,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1349,7 +1202,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1650,7 +1503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1789,153 +1642,6 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:56:46 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:GOQASy66</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Almeria</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Mirandes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
         <is>
           <t>No Sportsbet event matched this fixture.</t>
         </is>
@@ -2157,7 +1863,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2167,7 +1873,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2347,7 +2053,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2394,7 +2100,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2441,7 +2147,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2512,7 +2218,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:56:46 ACST</t>
+          <t>2026-05-04 07:11:13 ACST</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2254,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2266,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2278,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2302,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,52 +236,52 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.3636</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0596</t>
+          <t>1.0744</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2737</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3384</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -978,52 +978,52 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.3636</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0596</t>
+          <t>1.0744</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.3878</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2737</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3384</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:13 ACST</t>
+          <t>2026-05-04 07:24:35 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -246,12 +246,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.4202</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -261,27 +261,27 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0744</t>
+          <t>1.0714</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2737</t>
+          <t>0.2745</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3384</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.4202</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0744</t>
+          <t>1.0714</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3878</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2737</t>
+          <t>0.2745</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3384</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:24:35 ACST</t>
+          <t>2026-05-04 07:33:50 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,22 +166,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:n1pZG14F</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10394261</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>St Louis City SC</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4202</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0714</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2745</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,34 +301,34 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:2qevfSqS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -338,7 +338,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -707,22 +707,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0656</t>
+          <t>1.0704</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.1443</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0.2076</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6517</t>
+          <t>0.6487</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -908,32 +908,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -963,22 +963,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10394261</t>
+          <t>10411540</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>St Louis City SC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4202</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1003,37 +1003,37 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0714</t>
+          <t>1.058</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.3939</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2745</t>
+          <t>0.278</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.3282</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1055,22 +1055,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1110,77 +1110,77 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10411540</t>
+          <t>10390285</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.6944</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1.0704</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.3939</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.2076</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3282</t>
+          <t>0.6487</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1194,153 +1194,6 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 07:33:50 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>10390285</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Man City</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.2174</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.0656</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.1443</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.204</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.6517</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -1503,7 +1356,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1642,6 +1495,153 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-04 11:08:58 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>flashscore:2qevfSqS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>No Sportsbet event matched this fixture.</t>
         </is>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:33:50 ACST</t>
+          <t>2026-05-04 11:08:58 ACST</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,32 +166,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:08:58 ACST</t>
+          <t>2026-05-05 01:24:19 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>10411540</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.45</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>3.3</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.303</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0584</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2863</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.328</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,44 +301,44 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:08:58 ACST</t>
+          <t>2026-05-05 01:24:19 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -363,82 +363,82 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>10390285</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>Everton</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t>Man City</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>6.5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.44</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.6944</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0704</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2076</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.6487</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -448,304 +448,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:08:58 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>10411540</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.4167</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.3472</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.058</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.3939</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.278</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.3282</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:08:58 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>10390285</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Man City</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1.0704</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.1437</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.2076</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.6487</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -908,7 +614,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:08:58 ACST</t>
+          <t>2026-05-05 01:24:19 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -978,12 +684,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -993,12 +699,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1008,22 +714,22 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1.0584</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3939</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.2863</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3282</t>
+          <t>0.328</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1055,7 +761,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:08:58 ACST</t>
+          <t>2026-05-05 01:24:19 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1353,300 +1059,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:08:58 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>flashscore:n1pZG14F</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nottingham</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:08:58 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:2qevfSqS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Austin FC</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1905,7 +1317,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1915,14 +1327,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1944,53 +1356,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2053,7 +1418,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:08:58 ACST</t>
+          <t>2026-05-05 01:24:19 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2100,7 +1465,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:08:58 ACST</t>
+          <t>2026-05-05 01:24:19 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2110,12 +1475,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/betting/soccer/north-america/usa-major-league-soccer</t>
+          <t>/betting/soccer/united-kingdom/english-premier-league</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2125,12 +1490,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2139,53 +1504,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:08:58 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>/betting/soccer/united-kingdom/english-premier-league</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2218,7 +1536,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:08:58 ACST</t>
+          <t>2026-05-05 01:24:19 ACST</t>
         </is>
       </c>
     </row>
@@ -2254,7 +1572,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2266,7 +1584,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2278,7 +1596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2302,7 +1620,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:19 ACST</t>
+          <t>2026-05-05 01:28:24 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:19 ACST</t>
+          <t>2026-05-05 01:28:24 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:19 ACST</t>
+          <t>2026-05-05 01:28:24 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:19 ACST</t>
+          <t>2026-05-05 01:28:24 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1418,7 +1418,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:19 ACST</t>
+          <t>2026-05-05 01:28:24 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:19 ACST</t>
+          <t>2026-05-05 01:28:24 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:19 ACST</t>
+          <t>2026-05-05 01:28:24 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,32 +166,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:24 ACST</t>
+          <t>2026-05-06 01:40:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>16072838</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,259 +201,700 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Roda JC Kerkrade</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ready_for_phase_2</t>
+          <t>needs_settlement</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10411540</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0584</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2863</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>healthy</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>Phase 1 status was needs_settlement.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:24 ACST</t>
+          <t>2026-05-06 01:40:40 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:rTwrFuZR</t>
+          <t>16115678</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10390285</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Man City</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.0704</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.1437</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.2076</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6487</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
         </is>
       </c>
     </row>
@@ -611,300 +1052,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:24 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>10411540</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4082</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.303</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.3472</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.0584</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.3857</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.2863</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.328</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:24 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10390285</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Man City</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.6944</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.0704</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.1437</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.2076</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6487</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1213,6 +1360,741 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>16072838</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>needs_settlement</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Phase 1 status was needs_settlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>16115678</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:40 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1270,17 +2152,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1310,24 +2192,24 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1357,7 +2239,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1415,100 +2297,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:24 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>/betting/soccer/spain/spanish-la-liga</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:24 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>/betting/soccer/united-kingdom/english-premier-league</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1536,7 +2324,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:24 ACST</t>
+          <t>2026-05-06 01:40:40 ACST</t>
         </is>
       </c>
     </row>
@@ -1572,7 +2360,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1584,7 +2372,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1596,7 +2384,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1608,7 +2396,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1680,7 +2468,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1692,7 +2480,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Proceed with Phase 3 for ready_for_phase_3 rows.</t>
+          <t>No ready_for_phase_2 fixtures in Phase 1; rerun Phase 1 first.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -328,12 +328,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,12 +475,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -607,32 +607,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -754,145 +754,733 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>source_unverified</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Phase 1 status was source_unverified.</t>
         </is>
@@ -1363,7 +1951,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1510,7 +2098,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1525,12 +2113,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1545,12 +2133,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1657,7 +2245,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1672,12 +2260,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1692,12 +2280,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1804,32 +2392,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1839,12 +2427,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1951,145 +2539,733 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>source_unverified</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Phase 1 status was source_unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:45 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>source_unverified</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Phase 1 status was source_unverified.</t>
         </is>
@@ -2152,12 +3328,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2192,54 +3368,289 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2324,7 +3735,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:40 ACST</t>
+          <t>2026-05-07 01:36:45 ACST</t>
         </is>
       </c>
     </row>
@@ -2360,7 +3771,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2384,7 +3795,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2468,7 +3879,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,22 +166,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:I9QHhKRp</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10445137</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5263</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0704</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.4917</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2748</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.2336</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,19 +301,19 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -363,82 +363,82 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>10445218</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t>Girona</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>16.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.8</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0625</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0847</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.7375</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2048</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0576</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -448,19 +448,19 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -515,77 +515,77 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10445218</t>
+          <t>10445210</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.5714</t>
+          <t>0.9709</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.2632</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.2309</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.0655</t>
+          <t>1.0741</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.5363</t>
+          <t>0.9039</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.0846</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.0115</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -662,67 +662,67 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10445210</t>
+          <t>10445204</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.8197</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0496</t>
+          <t>1.0871</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.754</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.2722</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -809,67 +809,67 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10445204</t>
+          <t>10445212</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t>0.0769</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.7353</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.0597</t>
+          <t>1.0979</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2775</t>
+          <t>0.2602</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.2621</t>
+          <t>0.6697</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -956,67 +956,67 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10445212</t>
+          <t>10445211</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t>0.8475</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.0779</t>
+          <t>1.086</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.4418</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.3373</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2209</t>
+          <t>0.7804</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1098,82 +1098,82 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10445211</t>
+          <t/>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t/>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t/>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t/>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t/>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t/>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.2564</t>
+          <t/>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t/>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t/>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.0519</t>
+          <t/>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.2437</t>
+          <t/>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.2925</t>
+          <t/>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.4637</t>
+          <t/>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1183,19 +1183,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1250,67 +1250,67 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10445209</t>
+          <t>10445202</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t>0.8333</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1.0833</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.4735</t>
+          <t>0.0462</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.2705</t>
+          <t>0.1846</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>0.7692</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1397,77 +1397,77 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10445208</t>
+          <t>10445209</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t>0.0476</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.0518</t>
+          <t>1.0599</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.9435</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.2971</t>
+          <t>0.0449</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.3067</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1489,22 +1489,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1544,67 +1544,67 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10445202</t>
+          <t>10445146</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.4444</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1.0634</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.2867</t>
+          <t>0.4179</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3134</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.4505</t>
+          <t>0.2687</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1691,67 +1691,67 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10445146</t>
+          <t>10445141</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.4348</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.0711</t>
+          <t>1.062</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.4059</t>
+          <t>0.3693</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.3112</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.2829</t>
+          <t>0.3269</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1838,22 +1838,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10445141</t>
+          <t>10445122</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>US Cremonese</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1878,37 +1878,37 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.0679</t>
+          <t>1.0619</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.3924</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.3021</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.3405</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1930,22 +1930,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1985,77 +1985,77 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10445122</t>
+          <t>10469364</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>US Cremonese</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t>0.5236</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.0641</t>
+          <t>1.0593</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.3836</t>
+          <t>0.4943</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.3032</t>
+          <t>0.2697</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.3132</t>
+          <t>0.236</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2077,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2132,67 +2132,67 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10469364</t>
+          <t>10469368</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.5405</t>
+          <t>0.7353</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.2105</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.2309</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.0492</t>
+          <t>1.0791</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.5152</t>
+          <t>0.6814</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.2648</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.2201</t>
+          <t>0.1235</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2224,7 +2224,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2279,67 +2279,67 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10469368</t>
+          <t>10469363</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.7353</t>
+          <t>0.4348</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.2105</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.0634</t>
+          <t>1.0515</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.6915</t>
+          <t>0.4135</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.1979</t>
+          <t>0.2797</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.1106</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2371,7 +2371,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2426,67 +2426,67 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10469363</t>
+          <t>10469365</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.6803</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.0596</t>
+          <t>1.0621</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.6405</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2518,7 +2518,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2573,67 +2573,67 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10469365</t>
+          <t>10469357</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.5882</t>
+          <t>0.5236</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.2222</t>
+          <t>0.2778</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.0485</t>
+          <t>1.0514</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>0.498</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.2271</t>
+          <t>0.2378</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.2119</t>
+          <t>0.2642</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2665,7 +2665,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2720,67 +2720,67 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10469357</t>
+          <t>10469369</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3704</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.2564</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.0594</t>
+          <t>1.0561</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.2705</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.3788</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2812,7 +2812,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2867,67 +2867,67 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10469369</t>
+          <t>10469361</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.7812</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.1667</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.3846</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.0532</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.7417</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.2689</t>
+          <t>0.1583</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2959,7 +2959,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3009,82 +3009,82 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10469361</t>
+          <t/>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t/>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t/>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t/>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t/>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t/>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.7812</t>
+          <t/>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.1818</t>
+          <t/>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t/>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.0683</t>
+          <t/>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.7313</t>
+          <t/>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t/>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.0986</t>
+          <t/>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3094,19 +3094,19 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3156,82 +3156,82 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t/>
+          <t>10469366</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t/>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t/>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t/>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t/>
+          <t>4.2</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t/>
+          <t>2.05</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2381</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4878</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0592</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2248</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4605</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3241,34 +3241,34 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3308,67 +3308,67 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>10469366</t>
+          <t>10445213</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.7519</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.0595</t>
+          <t>1.067</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.7047</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>0.1704</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.4495</t>
+          <t>0.1249</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3400,22 +3400,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:I9QHhKRp</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3450,82 +3450,82 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10445213</t>
+          <t/>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t/>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t/>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t/>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t/>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t/>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t/>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.1667</t>
+          <t/>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t/>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.0609</t>
+          <t/>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t/>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.1571</t>
+          <t/>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.1178</t>
+          <t/>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
@@ -3701,22 +3701,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:I9QHhKRp</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3756,77 +3756,77 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10445137</t>
+          <t>10445218</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5263</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.0625</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0704</t>
+          <t>1.0847</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.4917</t>
+          <t>0.7375</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2748</t>
+          <t>0.2048</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.2336</t>
+          <t>0.0576</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3848,7 +3848,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3903,77 +3903,77 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10445218</t>
+          <t>10445210</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.5714</t>
+          <t>0.9709</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.2632</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2309</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.0655</t>
+          <t>1.0741</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.5363</t>
+          <t>0.9039</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.0846</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.0115</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3995,7 +3995,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4050,67 +4050,67 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10445210</t>
+          <t>10445204</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.8197</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.0496</t>
+          <t>1.0871</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.754</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.2722</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -4142,7 +4142,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4197,67 +4197,67 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10445204</t>
+          <t>10445212</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t>0.0769</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.7353</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0597</t>
+          <t>1.0979</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2775</t>
+          <t>0.2602</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.2621</t>
+          <t>0.6697</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -4289,7 +4289,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4344,67 +4344,67 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10445212</t>
+          <t>10445211</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t>0.8475</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.0779</t>
+          <t>1.086</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.4418</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3373</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.2209</t>
+          <t>0.7804</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -4436,7 +4436,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -4491,67 +4491,67 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10445211</t>
+          <t>10445202</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.2564</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t>0.8333</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.0519</t>
+          <t>1.0833</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.2437</t>
+          <t>0.0462</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2925</t>
+          <t>0.1846</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.4637</t>
+          <t>0.7692</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4618,97 +4618,97 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Vallecano</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10445209</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>Rayo Vallecano</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>10445209</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.0476</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1.0599</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.4735</t>
+          <t>0.9435</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.2705</t>
+          <t>0.0449</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>0.0116</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -4730,22 +4730,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4785,67 +4785,67 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10445208</t>
+          <t>10445146</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.4444</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.0518</t>
+          <t>1.0634</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.3962</t>
+          <t>0.4179</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.2971</t>
+          <t>0.3134</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.3067</t>
+          <t>0.2687</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4877,22 +4877,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4932,67 +4932,67 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10445202</t>
+          <t>10445141</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1.062</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.2867</t>
+          <t>0.3693</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.4505</t>
+          <t>0.3269</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5079,77 +5079,77 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10445146</t>
+          <t>10445122</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>US Cremonese</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.4348</t>
+          <t>0.4167</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.0711</t>
+          <t>1.0619</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.4059</t>
+          <t>0.3924</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.3112</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.2829</t>
+          <t>0.3038</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5171,22 +5171,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5226,67 +5226,67 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10445141</t>
+          <t>10469364</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.5236</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.3636</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.0679</t>
+          <t>1.0593</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.3574</t>
+          <t>0.4943</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.3021</t>
+          <t>0.2697</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.3405</t>
+          <t>0.236</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -5318,22 +5318,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5373,77 +5373,77 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10445122</t>
+          <t>10469368</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>US Cremonese</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t>0.7353</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2105</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.0641</t>
+          <t>1.0791</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.3836</t>
+          <t>0.6814</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.3032</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.3132</t>
+          <t>0.1235</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -5465,7 +5465,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5500,12 +5500,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -5520,67 +5520,67 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10469364</t>
+          <t>10469363</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.5405</t>
+          <t>0.4348</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.2309</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.0492</t>
+          <t>1.0515</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.5152</t>
+          <t>0.4135</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.2648</t>
+          <t>0.2797</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.2201</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -5612,7 +5612,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -5667,67 +5667,67 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10469368</t>
+          <t>10469365</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.7353</t>
+          <t>0.6803</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.2105</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.0634</t>
+          <t>1.0621</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.6915</t>
+          <t>0.6405</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.1979</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.1106</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -5759,7 +5759,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -5814,67 +5814,67 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10469363</t>
+          <t>10469357</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.5236</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.2778</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.0596</t>
+          <t>1.0514</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.3701</t>
+          <t>0.498</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2378</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.2642</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5961,67 +5961,67 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10469365</t>
+          <t>10469369</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.5882</t>
+          <t>0.3704</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.2222</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.0485</t>
+          <t>1.0561</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>0.3507</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.2271</t>
+          <t>0.2705</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.2119</t>
+          <t>0.3788</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -6053,7 +6053,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -6108,67 +6108,67 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10469357</t>
+          <t>10469361</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7812</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.2564</t>
+          <t>0.1667</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.0594</t>
+          <t>1.0532</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>0.7417</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1583</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -6200,7 +6200,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -6255,67 +6255,67 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10469369</t>
+          <t>10469366</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.2381</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.3846</t>
+          <t>0.4878</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.0592</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.2689</t>
+          <t>0.2248</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.4605</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -6347,22 +6347,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6402,22 +6402,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10469361</t>
+          <t>10445213</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.7812</t>
+          <t>0.7519</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6442,27 +6442,27 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.0683</t>
+          <t>1.067</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.7313</t>
+          <t>0.7047</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1704</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.0986</t>
+          <t>0.1249</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -6486,300 +6486,6 @@
         </is>
       </c>
       <c r="AC20" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:55:18 ACST</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>flashscore:44Vsqc0E</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>10469366</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0.3333</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>0.4762</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1.0595</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0.3146</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>0.236</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>0.4495</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-05-18 01:55:18 ACST</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>flashscore:SduXBE3E</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>10445213</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0.7692</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0.1667</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1.0609</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0.725</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>0.1571</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>0.1178</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -6942,7 +6648,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6977,7 +6683,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7089,145 +6795,439 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>flashscore:llRR0leD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:02:31 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Paris FC</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>PSG</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>unmatched_market</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:02:31 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>flashscore:I9QHhKRp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>No Sportsbet event matched this fixture.</t>
         </is>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7639,7 +7639,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7733,7 +7733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 01:55:18 ACST</t>
+          <t>2026-05-18 04:02:31 ACST</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,22 +166,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>10445146</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>Torino</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>5.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>34.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.8696</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0294</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0808</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.8046</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1682</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0272</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,34 +301,34 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -338,7 +338,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -368,77 +368,77 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10445218</t>
+          <t>10445141</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>0.0556</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.2381</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.2222</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.0625</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.0847</t>
+          <t>1.0937</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.7375</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2048</t>
+          <t>0.2177</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.0576</t>
+          <t>0.7315</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -460,22 +460,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -515,77 +515,77 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10445210</t>
+          <t>10445122</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>US Cremonese</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.9709</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.8475</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.0741</t>
+          <t>1.086</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.9039</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0846</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0115</t>
+          <t>0.7804</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -607,22 +607,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -662,67 +662,67 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10445204</t>
+          <t>10469364</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.8197</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.5464</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0871</t>
+          <t>1.0754</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5081</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.1691</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -754,22 +754,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -809,67 +809,67 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10445212</t>
+          <t>10469368</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0769</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.7353</t>
+          <t>0.5714</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.0979</t>
+          <t>1.0865</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.1673</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2602</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.6697</t>
+          <t>0.5259</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -901,22 +901,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -951,82 +951,82 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10445211</t>
+          <t/>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t/>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t/>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t/>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t/>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t/>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.8475</t>
+          <t/>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t/>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.0355</t>
+          <t/>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t/>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.7804</t>
+          <t/>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1036,34 +1036,34 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1098,82 +1098,82 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t/>
+          <t>10469365</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t/>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t/>
+          <t>Lens</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t/>
+          <t>81.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t/>
+          <t>61.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0287</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.012</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9721</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1183,34 +1183,34 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1250,67 +1250,67 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10445202</t>
+          <t>10469357</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0244</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.8333</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.0833</t>
+          <t>1.0367</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0462</t>
+          <t>0.9646</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.1846</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t>0.0119</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1342,22 +1342,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1397,77 +1397,77 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10445209</t>
+          <t>10469361</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.5128</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.4545</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1.0923</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.4695</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.4161</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.1144</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.0476</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.0123</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.0599</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.9435</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.0449</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.0116</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>substring</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.846</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1489,22 +1489,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1539,82 +1539,82 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10445146</t>
+          <t/>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t/>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t/>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t/>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.4444</t>
+          <t/>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.0634</t>
+          <t/>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.4179</t>
+          <t/>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t/>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.2687</t>
+          <t/>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1624,34 +1624,34 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1691,67 +1691,67 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10445141</t>
+          <t>10469366</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.0294</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.0952</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.9524</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>1.077</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.3693</t>
+          <t>0.0273</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.0884</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.3269</t>
+          <t>0.8843</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1783,22 +1783,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1838,77 +1838,77 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10445122</t>
+          <t>10445213</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>US Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.8772</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.0526</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1.0619</t>
+          <t>1.0836</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.3924</t>
+          <t>0.8095</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.0485</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1930,22 +1930,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1980,82 +1980,82 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10469364</t>
+          <t/>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t/>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t/>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t/>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.5236</t>
+          <t/>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t/>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.0593</t>
+          <t/>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.4943</t>
+          <t/>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.2697</t>
+          <t/>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t/>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2065,34 +2065,34 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2127,82 +2127,82 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>10469368</t>
+          <t/>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t/>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t/>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t/>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t/>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t/>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.7353</t>
+          <t/>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.2105</t>
+          <t/>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t/>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.0791</t>
+          <t/>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.6814</t>
+          <t/>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t/>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.1235</t>
+          <t/>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2212,34 +2212,34 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2274,82 +2274,82 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10469363</t>
+          <t/>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t/>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t/>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t/>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t/>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.4348</t>
+          <t/>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t/>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.0515</t>
+          <t/>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.4135</t>
+          <t/>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.2797</t>
+          <t/>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.3068</t>
+          <t/>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,34 +2359,34 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2421,82 +2421,82 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10469365</t>
+          <t/>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t/>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t/>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t/>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t/>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t/>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.6803</t>
+          <t/>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t/>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.1818</t>
+          <t/>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1.0621</t>
+          <t/>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.6405</t>
+          <t/>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t/>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t/>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2506,34 +2506,34 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2568,82 +2568,82 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>10469357</t>
+          <t/>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t/>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t/>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t/>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t/>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t/>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.5236</t>
+          <t/>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t/>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t/>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.0514</t>
+          <t/>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t/>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.2378</t>
+          <t/>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.2642</t>
+          <t/>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2653,34 +2653,34 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2715,82 +2715,82 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10469369</t>
+          <t/>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t/>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t/>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t/>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t/>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.3704</t>
+          <t/>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t/>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.0561</t>
+          <t/>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.3507</t>
+          <t/>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.2705</t>
+          <t/>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.3788</t>
+          <t/>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2800,34 +2800,34 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2862,82 +2862,82 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>10469361</t>
+          <t/>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t/>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t/>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t/>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t/>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t/>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.7812</t>
+          <t/>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.1667</t>
+          <t/>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t/>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.0532</t>
+          <t/>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.7417</t>
+          <t/>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.1583</t>
+          <t/>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t/>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2947,34 +2947,34 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3106,22 +3106,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3156,82 +3156,82 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>10469366</t>
+          <t/>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t/>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t/>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t/>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t/>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t/>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t/>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.0592</t>
+          <t/>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t/>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.2248</t>
+          <t/>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0.4605</t>
+          <t/>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3241,34 +3241,34 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3303,82 +3303,82 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>10445213</t>
+          <t/>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t/>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t/>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t/>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t/>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t/>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.7519</t>
+          <t/>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.1818</t>
+          <t/>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t/>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t/>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.7047</t>
+          <t/>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.1704</t>
+          <t/>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.1249</t>
+          <t/>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3388,19 +3388,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3701,22 +3701,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3756,77 +3756,77 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10445218</t>
+          <t>10445146</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.8696</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2222</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0625</t>
+          <t>0.0294</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0847</t>
+          <t>1.0808</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.7375</t>
+          <t>0.8046</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2048</t>
+          <t>0.1682</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0576</t>
+          <t>0.0272</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3848,22 +3848,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3903,67 +3903,67 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10445210</t>
+          <t>10445141</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.9709</t>
+          <t>0.0556</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.2381</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.0123</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.0741</t>
+          <t>1.0937</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.9039</t>
+          <t>0.0508</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0846</t>
+          <t>0.2177</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.0115</t>
+          <t>0.7315</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -3995,22 +3995,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4050,77 +4050,77 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10445204</t>
+          <t>10445122</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>US Cremonese</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.8197</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.8475</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.0871</t>
+          <t>1.086</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.0355</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.7804</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4142,22 +4142,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4197,67 +4197,67 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10445212</t>
+          <t>10469364</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0769</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.5464</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7353</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.0979</t>
+          <t>1.0754</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2602</t>
+          <t>0.5081</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6697</t>
+          <t>0.1691</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -4289,22 +4289,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4344,67 +4344,67 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10445211</t>
+          <t>10469368</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.1818</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.8475</t>
+          <t>0.5714</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1.0865</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0355</t>
+          <t>0.1673</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.7804</t>
+          <t>0.5259</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -4436,22 +4436,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -4491,67 +4491,67 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10445202</t>
+          <t>10469365</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0123</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0164</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.8333</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1.0833</t>
+          <t>1.0287</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.0462</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.1846</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t>0.9721</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -4583,22 +4583,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4638,17 +4638,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10445209</t>
+          <t>10469357</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.0476</t>
+          <t>0.0244</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -4683,32 +4683,32 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1.0599</t>
+          <t>1.0367</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.9435</t>
+          <t>0.9646</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.0235</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.0116</t>
+          <t>0.0119</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -4730,22 +4730,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4785,67 +4785,67 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10445146</t>
+          <t>10469361</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.4444</t>
+          <t>0.5128</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.4545</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1.0634</t>
+          <t>1.0923</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.4179</t>
+          <t>0.4695</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t>0.4161</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.2687</t>
+          <t>0.1144</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4877,22 +4877,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4932,67 +4932,67 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10445141</t>
+          <t>10469366</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.0294</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.0952</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.9524</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>1.077</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.3693</t>
+          <t>0.0273</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.0884</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.3269</t>
+          <t>0.8843</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -5024,22 +5024,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5079,77 +5079,77 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10445122</t>
+          <t>10445213</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>US Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.4167</t>
+          <t>0.8772</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.0526</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.0619</t>
+          <t>1.0836</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.3924</t>
+          <t>0.8095</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.3038</t>
+          <t>0.0485</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5163,1329 +5163,6 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>flashscore:prPnPy9r</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>10469364</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0.5236</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0.2857</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.0593</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0.4943</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0.2697</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>0.236</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>flashscore:IXv8WJG8</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>10469368</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0.7353</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0.2105</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>0.1333</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1.0791</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0.6814</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0.1235</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>flashscore:r1cGQTSk</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>10469363</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0.4348</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>0.3226</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1.0515</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0.4135</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0.2797</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>0.3068</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>flashscore:OhrGQlpm</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>10469365</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0.6803</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>0.1818</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1.0621</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0.6405</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0.1883</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>0.1712</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>flashscore:xbwdLg87</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>10469357</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0.5236</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>0.2778</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1.0514</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0.498</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0.2378</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0.2642</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>flashscore:z9FNO7c2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>10469369</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0.3704</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0.2857</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1.0561</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0.3507</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0.2705</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>0.3788</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>flashscore:QcrGUcoL</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>10469361</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0.7812</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0.1667</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>0.1053</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1.0532</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0.7417</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0.1583</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>flashscore:44Vsqc0E</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>10469366</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0.3333</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0.2381</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>0.4878</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1.0592</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0.3147</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0.2248</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>0.4605</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-05-18 04:02:31 ACST</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>flashscore:SduXBE3E</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>10445213</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Betis</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0.7519</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0.1818</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>0.1333</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1.067</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0.7047</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.1704</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>0.1249</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -6648,22 +5325,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6673,7 +5350,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6683,12 +5360,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6795,22 +5472,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6820,7 +5497,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6830,12 +5507,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6942,22 +5619,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6967,7 +5644,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6977,12 +5654,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -7089,145 +5766,1468 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>flashscore:n12plBB7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>flashscore:0OhvAhYQ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>flashscore:K8ZA4Wel</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>flashscore:YFVo6qXh</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>flashscore:C0sw852t</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>flashscore:llRR0leD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>flashscore:ttZg4N15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>flashscore:hMXI2AQ0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vallecano</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>flashscore:z9FNO7c2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-18 05:54:11 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>flashscore:I9QHhKRp</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Bologna</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>unmatched_market</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>No Sportsbet event matched this fixture.</t>
         </is>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7639,7 +7639,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7733,7 +7733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:02:31 ACST</t>
+          <t>2026-05-18 05:54:11 ACST</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -181,7 +181,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:rZdvkkLE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10472119</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3515</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2971</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3515</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,19 +301,19 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:lnSvmTkR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,52 +530,52 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.9346</t>
+          <t>0.9091</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0769</t>
+          <t>0.0952</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.0543</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8901</t>
+          <t>0.8623</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0732</t>
+          <t>0.0903</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0367</t>
+          <t>0.0474</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -761,32 +761,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -816,67 +816,67 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10472119</t>
+          <t>10446230</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.9091</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.0952</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1.0543</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3515</t>
+          <t>0.8623</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2971</t>
+          <t>0.0903</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.3515</t>
+          <t>0.0474</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -900,153 +900,6 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 09:53:53 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10446230</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.9346</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0769</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.0385</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.8901</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.0732</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.0367</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -1209,7 +1062,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1348,6 +1201,153 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-18 13:53:53 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>flashscore:lnSvmTkR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>No Sportsbet event matched this fixture.</t>
         </is>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:53:53 ACST</t>
+          <t>2026-05-18 13:53:53 ACST</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,52 +530,52 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.9091</t>
+          <t>0.9259</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0952</t>
+          <t>0.0833</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.0543</t>
+          <t>1.0477</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8623</t>
+          <t>0.8837</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0903</t>
+          <t>0.0795</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0474</t>
+          <t>0.0367</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -831,52 +831,52 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.9091</t>
+          <t>0.9259</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0952</t>
+          <t>0.0833</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0543</t>
+          <t>1.0477</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8623</t>
+          <t>0.8837</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0903</t>
+          <t>0.0795</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0474</t>
+          <t>0.0367</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1062,7 +1062,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:53:53 ACST</t>
+          <t>2026-05-18 17:53:54 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,32 +166,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:53:54 ACST</t>
+          <t>2026-05-19 01:53:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>10446230</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.08</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>11.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>23.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.9259</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0435</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0603</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.8732</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0857</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.041</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,304 +301,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:53:54 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:53:54 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>10446230</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.9259</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0833</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.0385</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.0477</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.8837</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.0795</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.0367</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -761,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:53:54 ACST</t>
+          <t>2026-05-19 01:53:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -836,12 +542,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -851,32 +557,32 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0833</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.0435</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0477</t>
+          <t>1.0603</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8837</t>
+          <t>0.8732</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0795</t>
+          <t>0.0857</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0367</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1059,300 +765,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:53:54 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>flashscore:rZdvkkLE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Inter Miami</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:53:54 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1564,24 +976,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1603,53 +1015,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1712,7 +1077,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:53:54 ACST</t>
+          <t>2026-05-19 01:53:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1722,12 +1087,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/betting/soccer/north-america/usa-major-league-soccer</t>
+          <t>/betting/soccer/united-kingdom/english-premier-league</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1737,12 +1102,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1751,53 +1116,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:53:54 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>/betting/soccer/united-kingdom/english-premier-league</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1830,7 +1148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:53:54 ACST</t>
+          <t>2026-05-19 01:53:43 ACST</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1184,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1196,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1208,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1232,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:43 ACST</t>
+          <t>2026-05-19 17:59:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -181,17 +181,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -221,90 +221,237 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10446230</t>
+          <t>10485206</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.9259</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.2309</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0435</t>
+          <t>0.6061</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0603</t>
+          <t>1.0544</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8732</t>
+          <t>0.2062</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0857</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.5748</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:04 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10477114</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5263</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.2703</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.0466</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5029</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.2583</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.2389</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>ready_for_phase_3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -467,7 +614,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:43 ACST</t>
+          <t>2026-05-19 17:59:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,17 +629,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,12 +649,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -522,90 +669,237 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10446230</t>
+          <t>10485206</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.9259</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.2309</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0435</t>
+          <t>0.6061</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0603</t>
+          <t>1.0544</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8732</t>
+          <t>0.2062</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0857</t>
+          <t>0.219</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.5748</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:04 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10477114</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5263</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.2703</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.0466</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5029</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.2583</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.2389</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>ready_for_phase_3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -981,12 +1275,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1077,7 +1371,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:43 ACST</t>
+          <t>2026-05-19 17:59:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1102,12 +1396,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1148,7 +1442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:53:43 ACST</t>
+          <t>2026-05-19 17:59:04 ACST</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1490,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1502,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1514,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:04 ACST</t>
+          <t>2026-05-20 01:56:05 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,52 +236,52 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2309</t>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6061</t>
+          <t>0.6369</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0544</t>
+          <t>1.0591</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.2062</t>
+          <t>0.1888</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.2098</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5748</t>
+          <t>0.6014</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:04 ACST</t>
+          <t>2026-05-20 01:56:05 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -383,52 +383,52 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.5263</t>
+          <t>0.4878</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.0466</t>
+          <t>1.0676</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.5029</t>
+          <t>0.4569</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2583</t>
+          <t>0.2755</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2389</t>
+          <t>0.2676</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:04 ACST</t>
+          <t>2026-05-20 01:56:05 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -684,52 +684,52 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2309</t>
+          <t>0.2222</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6061</t>
+          <t>0.6369</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0544</t>
+          <t>1.0591</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.2062</t>
+          <t>0.1888</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.2098</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5748</t>
+          <t>0.6014</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:04 ACST</t>
+          <t>2026-05-20 01:56:05 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -831,52 +831,52 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.5263</t>
+          <t>0.4878</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.0466</t>
+          <t>1.0676</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.5029</t>
+          <t>0.4569</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2583</t>
+          <t>0.2755</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2389</t>
+          <t>0.2676</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:04 ACST</t>
+          <t>2026-05-20 01:56:05 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:04 ACST</t>
+          <t>2026-05-20 01:56:05 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:05 ACST</t>
+          <t>2026-05-20 05:55:36 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -181,7 +181,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -221,77 +221,77 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10485206</t>
+          <t>10477114</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.7692</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2222</t>
+          <t>0.2381</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6369</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0591</t>
+          <t>1.0982</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.1888</t>
+          <t>0.7004</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2098</t>
+          <t>0.2168</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6014</t>
+          <t>0.0828</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:05 ACST</t>
+          <t>2026-05-20 05:55:36 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -338,7 +338,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -363,82 +363,82 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10477114</t>
+          <t/>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t/>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t/>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t/>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.4878</t>
+          <t/>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t/>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.0676</t>
+          <t/>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.4569</t>
+          <t/>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2755</t>
+          <t/>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2676</t>
+          <t/>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -448,12 +448,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:05 ACST</t>
+          <t>2026-05-20 05:55:36 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -669,77 +669,77 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10485206</t>
+          <t>10477114</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.7692</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2222</t>
+          <t>0.2381</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6369</t>
+          <t>0.0909</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0591</t>
+          <t>1.0982</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.1888</t>
+          <t>0.7004</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2098</t>
+          <t>0.2168</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6014</t>
+          <t>0.0828</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>alias</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -753,153 +753,6 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-20 01:56:05 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:Uu6uknGb</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>04:45</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Tottenham</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10477114</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tottenham</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.4878</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.2857</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.0676</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.4569</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.2755</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.2676</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -1059,6 +912,153 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-20 05:55:36 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>flashscore:rkXMW40U</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:05 ACST</t>
+          <t>2026-05-20 05:55:36 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:05 ACST</t>
+          <t>2026-05-20 05:55:36 ACST</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,32 +166,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:36 ACST</t>
+          <t>2026-05-20 09:56:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -221,67 +221,67 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10477114</t>
+          <t>10497512</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t>0.5556</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.2632</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0982</t>
+          <t>1.0688</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.7004</t>
+          <t>0.5198</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2168</t>
+          <t>0.2339</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0828</t>
+          <t>0.2463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -313,32 +313,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:36 ACST</t>
+          <t>2026-05-20 09:56:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2475106</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -363,97 +363,685 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>10497513</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.9</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>3.9</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>3.5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5263</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2564</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.0684</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4926</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2674</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10498423</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.3636</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.2857</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.4082</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1.0575</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.3438</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.2702</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.386</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10498389</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.5714</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.2703</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.2105</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.0522</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5431</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.2569</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.2001</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279764</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>unmatched_market</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10498404</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.4444</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.3077</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.303</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.0551</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.4212</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.2916</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.2872</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>substring</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
@@ -614,32 +1202,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:36 ACST</t>
+          <t>2026-05-20 09:56:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -649,12 +1237,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -669,67 +1257,67 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10477114</t>
+          <t>10497512</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.7692</t>
+          <t>0.5556</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2381</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0909</t>
+          <t>0.2632</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0982</t>
+          <t>1.0688</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.7004</t>
+          <t>0.5198</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2168</t>
+          <t>0.2339</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0828</t>
+          <t>0.2463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -753,6 +1341,594 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>thesportsdb:2475106</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10497513</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FC Utrecht</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5263</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.2564</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.2857</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.0684</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.4926</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.2674</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10498423</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.3636</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.2857</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.4082</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1.0575</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.3438</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.2702</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.386</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10498389</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.5714</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.2703</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.2105</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1.0522</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5431</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.2569</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.2001</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10498404</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.4444</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.3077</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.303</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1.0551</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.4212</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.2916</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.2872</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>substring</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -915,32 +2091,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:36 ACST</t>
+          <t>2026-05-20 09:56:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2279764</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -950,12 +2126,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1270,7 +2446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1280,35 +2456,129 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1371,7 +2641,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:36 ACST</t>
+          <t>2026-05-20 09:56:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1381,12 +2651,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/betting/soccer/united-kingdom/english-premier-league</t>
+          <t>/betting/soccer/rest-of-europe/dutch-eredivisie</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1396,12 +2666,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1410,6 +2680,100 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>/betting/soccer/spain/spanish-la-liga</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:56:09 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>/betting/soccer/italy/italian-serie-a</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1442,7 +2806,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:55:36 ACST</t>
+          <t>2026-05-20 09:56:09 ACST</t>
         </is>
       </c>
     </row>
@@ -1478,7 +2842,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1490,7 +2854,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1502,7 +2866,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1514,7 +2878,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,22 +166,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -201,12 +201,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>10495406</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.47</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>6.5</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.6803</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3125</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>1.1466</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5933</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2725</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,34 +301,34 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -363,82 +363,82 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10495406</t>
+          <t/>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t/>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t/>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t/>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.4545</t>
+          <t/>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.1003</t>
+          <t/>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t/>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t/>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4131</t>
+          <t/>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -448,19 +448,19 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -510,82 +510,82 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>10483693</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>Brann</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>3.0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>1.91</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5236</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>1.151</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2896</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2555</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4549</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>substring</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.945</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>No Sportsbet event matched this fixture.</t>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -657,82 +657,82 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10483693</t>
+          <t/>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t/>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t/>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t/>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5236</t>
+          <t/>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.088</t>
+          <t/>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t/>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2484</t>
+          <t/>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.4812</t>
+          <t/>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.6803</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1003,27 +1003,27 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.4545</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.1003</t>
+          <t>1.1466</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.5933</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>0.2725</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4131</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1125,14 +1125,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -1140,14 +1140,14 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>0.3333</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>0.2941</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.2703</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>0.5236</t>
@@ -1155,22 +1155,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.088</t>
+          <t>1.151</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.2703</t>
+          <t>0.2896</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2484</t>
+          <t>0.2555</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4812</t>
+          <t>0.4549</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2006,7 +2006,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:55:46 ACST</t>
+          <t>2026-05-21 03:42:12 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10495406</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.6803</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.1538</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.1466</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5933</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2725</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,19 +301,19 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -328,7 +328,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -338,7 +338,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -510,82 +510,82 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10483693</t>
+          <t/>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t/>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t/>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t/>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t/>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t/>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5236</t>
+          <t/>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t/>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.2896</t>
+          <t/>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.2555</t>
+          <t/>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.4549</t>
+          <t/>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -905,300 +905,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-21 03:42:12 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>flashscore:rJKJ2MZP</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>GAIS</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Hammarby</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>10495406</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>GAIS</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Hammarby</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.6803</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.3125</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.1466</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.5933</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.2725</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.1341</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 03:42:12 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>flashscore:0A1Nl9Wh</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10483693</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Aalesunds</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.3333</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.5236</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.151</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.2896</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.2555</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.4549</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>substring</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.945</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1356,22 +1062,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1381,7 +1087,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1391,12 +1097,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1503,7 +1209,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1518,130 +1224,424 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>flashscore:0A1Nl9Wh</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aalesund</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:57:29 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Eliteserien</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>flashscore:YobepuNG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lilleström</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-21 05:57:29 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Eliteserien</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Bodo/Glimt</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>unmatched_market</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>No Sportsbet event matched this fixture.</t>
         </is>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2006,7 +2006,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:42:12 ACST</t>
+          <t>2026-05-21 05:57:29 ACST</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:12 ACST</t>
+          <t>2026-05-21 18:22:06 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:12 ACST</t>
+          <t>2026-05-21 18:22:06 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:12 ACST</t>
+          <t>2026-05-21 18:22:06 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:12 ACST</t>
+          <t>2026-05-21 18:22:06 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:06 ACST</t>
+          <t>2026-05-22 01:58:46 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -246,12 +246,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.3704</t>
+          <t>0.4762</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -261,27 +261,27 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1.1018</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3389</t>
+          <t>0.4322</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2952</t>
+          <t>0.2928</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:06 ACST</t>
+          <t>2026-05-22 01:58:46 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -547,12 +547,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.3704</t>
+          <t>0.4762</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -562,27 +562,27 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1.1018</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.3389</t>
+          <t>0.4322</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2952</t>
+          <t>0.2928</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:06 ACST</t>
+          <t>2026-05-22 01:58:46 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:06 ACST</t>
+          <t>2026-05-22 01:58:46 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:58:46 ACST</t>
+          <t>2026-05-22 04:29:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -191,7 +191,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -216,82 +216,82 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Sportsbet</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10495548</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4762</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.1018</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.4322</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2928</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -301,12 +301,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Clean Phase 2 odds.</t>
+          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
@@ -464,153 +464,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-22 01:58:46 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>02:30</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>10495548</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4762</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.3226</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.303</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>1.1018</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.4322</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.2928</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.275</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -765,6 +618,153 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-22 04:29:27 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>flashscore:zHabevSa</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -986,12 +986,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:58:46 ACST</t>
+          <t>2026-05-22 04:29:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:58:46 ACST</t>
+          <t>2026-05-22 04:29:27 ACST</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,147 +166,441 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:27 ACST</t>
+          <t>2026-05-22 17:56:57 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>flashscore:fXvLSp0T</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>unmatched_market</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>No Sportsbet event matched this fixture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:56:57 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10500468</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Djurgardens</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.7143</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.2174</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.1538</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.0855</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.2003</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>substring</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:56:57 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10498423</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.3636</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.2941</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1.0577</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.3438</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.2781</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.3782</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
@@ -464,6 +758,300 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:56:57 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10500468</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Djurgardens</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.7143</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.2174</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.1538</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1.0855</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.2003</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>substring</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:56:57 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Australia/Adelaide</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10498423</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.3636</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.2941</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.0577</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.3438</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.2781</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3782</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -621,22 +1209,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:27 ACST</t>
+          <t>2026-05-22 17:56:57 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>J1 League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:zHabevSa</t>
+          <t>flashscore:fXvLSp0T</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -646,7 +1234,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -656,12 +1244,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Machida</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Urawa</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -986,35 +1574,129 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1077,7 +1759,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:27 ACST</t>
+          <t>2026-05-22 17:56:57 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,6 +1798,100 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:56:57 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>/betting/soccer/asia/japanese-j1-league</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:56:57 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sportsbet</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>/betting/soccer/italy/italian-serie-a</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1148,7 +1924,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:27 ACST</t>
+          <t>2026-05-22 17:56:57 ACST</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1972,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1984,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1996,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -166,7 +166,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -313,7 +313,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,7 +460,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1853,7 +1853,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:56:57 ACST</t>
+          <t>2026-05-22 18:58:48 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
+++ b/docs/agent-system/outputs/Phase2_Odds_Slate.xlsx
@@ -49,115 +49,150 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>timezone</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>home_team_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>home_logo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>home_goals</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>away_team_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>away_logo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>away_goals</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>phase1_status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>odds_source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>sportsbet_event_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sportsbet_home_name</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>sportsbet_away_name</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_odds</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>draw_odds</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>away_odds</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>implied_home</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>implied_draw</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>implied_away</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>fair_home</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fair_draw</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>fair_away</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>match_method</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>match_score</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>source_health</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>phase2_status</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>phase2_notes</t>
         </is>
@@ -166,439 +201,362 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:58:48 ACST</t>
+          <t>2026-06-17 01:43:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:fXvLSp0T</t>
+          <t>thesportsdb:2391760</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Machida</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>136516</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/gyfn811591973155.png</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>136143</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/slayb01780546342.png</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>Sportsbet</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>10425320</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>Norway</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.15</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>0.4651</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
+          <t>0.3077</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>1.0585</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.4394</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.2699</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.2907</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ready_for_phase_3</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Clean Phase 2 odds.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:58:48 ACST</t>
+          <t>2026-06-17 01:43:32 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>thesportsdb:2391759</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Djurgarden</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>140145</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/59fo2s1742100034.png</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>134516</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/rrwpry1455460218.png</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Sportsbet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10500468</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Djurgardens</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Brommapojkarna</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>10425306</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.7143</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.2174</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0.1538</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>1.0855</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.658</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.2003</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.1417</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>substring</t>
-        </is>
-      </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>0.2439</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>0.6667</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1.0644</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.1445</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.2291</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6264</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>ready_for_phase_3</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Clean Phase 2 odds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-22 18:58:48 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>flashscore:ln2VQVwR</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>04:15</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>10498423</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.3636</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.2941</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>1.0577</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.3438</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.2781</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.3782</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>ready_for_phase_3</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -644,115 +602,150 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>timezone</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>home_team_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>home_logo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>home_goals</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>away_team_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>away_logo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>away_goals</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>phase1_status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>odds_source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>sportsbet_event_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sportsbet_home_name</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>sportsbet_away_name</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_odds</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>draw_odds</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>away_odds</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>implied_home</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>implied_draw</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>implied_away</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>fair_home</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fair_draw</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>fair_away</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>match_method</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>match_score</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>source_health</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>phase2_status</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>phase2_notes</t>
         </is>
@@ -761,145 +754,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:58:48 ACST</t>
+          <t>2026-06-17 01:43:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>thesportsdb:2391760</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Djurgarden</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>136516</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/gyfn811591973155.png</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>136143</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/slayb01780546342.png</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Sportsbet</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>10500468</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Djurgardens</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Brommapojkarna</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.7143</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>10425320</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.1538</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1.0855</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2003</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>substring</t>
+          <t>0.4651</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
+          <t>0.3077</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>1.0585</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.4394</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.2699</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.2907</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>ready_for_phase_3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -908,145 +936,180 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:58:48 ACST</t>
+          <t>2026-06-17 01:43:32 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>thesportsdb:2391759</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Australia/Adelaide</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>140145</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/59fo2s1742100034.png</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>134516</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://r2.thesportsdb.com/images/media/team/badge/rrwpry1455460218.png</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>ready_for_phase_2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Sportsbet</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10498423</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.3636</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>10425306</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1.0577</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2781</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3782</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>0.1538</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.2439</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6667</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1.0644</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.1445</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.2291</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6264</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>ready_for_phase_3</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Clean Phase 2 odds.</t>
         </is>
@@ -1092,264 +1155,152 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>timezone</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>home_team_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>home_logo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>home_goals</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>away_team_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>away_logo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>away_goals</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>phase1_status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>odds_source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>sportsbet_event_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sportsbet_home_name</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>sportsbet_away_name</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_odds</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>draw_odds</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>away_odds</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>implied_home</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>implied_draw</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>implied_away</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>fair_home</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fair_draw</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>fair_away</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>match_method</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>match_score</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>source_health</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>phase2_status</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>phase2_notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-22 18:58:48 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>J1 League</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>flashscore:fXvLSp0T</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Australia/Adelaide</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Machida</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Urawa</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ready_for_phase_2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>unmatched_market</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>No Sportsbet event matched this fixture.</t>
         </is>
       </c>
     </row>
@@ -1393,115 +1344,150 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>timezone</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>home_team_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>home_logo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>home_goals</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>away</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>away_team_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>away_logo</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>away_goals</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>phase1_status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>odds_source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>sportsbet_event_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sportsbet_home_name</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>sportsbet_away_name</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_odds</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>draw_odds</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>away_odds</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>implied_home</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>implied_draw</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>implied_away</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>fair_home</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fair_draw</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>fair_away</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>match_method</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>match_score</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>source_health</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>phase2_status</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>phase2_notes</t>
         </is>
@@ -1564,17 +1550,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1603,100 +1589,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>J1 League</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1759,7 +1651,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:58:48 ACST</t>
+          <t>2026-06-17 01:43:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1769,12 +1661,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/betting/soccer/rest-of-europe/swedish-allsvenskan</t>
+          <t>/betting/soccer/world-cup/mens-world-cup</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1784,12 +1676,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>56</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1798,100 +1690,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-22 18:58:48 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>J1 League</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>/betting/soccer/asia/japanese-j1-league</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-22 18:58:48 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Sportsbet</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>/betting/soccer/italy/italian-serie-a</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>healthy</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1924,7 +1722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:58:48 ACST</t>
+          <t>2026-06-17 01:43:32 ACST</t>
         </is>
       </c>
     </row>
@@ -1955,43 +1753,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>phase1_input_rows</t>
+          <t>target_dates</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>phase1_ready_rows</t>
+          <t>phase1_input_rows</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>phase2_total_rows</t>
+          <t>phase1_ready_rows</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ready_for_phase_3</t>
+          <t>phase2_total_rows</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2003,19 +1801,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unmatched_market</t>
+          <t>ready_for_phase_3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>partial_market</t>
+          <t>unmatched_market</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2027,7 +1825,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>implausible_overround</t>
+          <t>partial_market</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2039,7 +1837,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>low_match_confidence</t>
+          <t>implausible_overround</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2051,7 +1849,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source_blocked</t>
+          <t>low_match_confidence</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +1861,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>source_blocked</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2075,10 +1873,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>next_action</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Proceed with Phase 3 for ready_for_phase_3 rows.</t>
         </is>
